--- a/App Store/Promotional Text.xlsx
+++ b/App Store/Promotional Text.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mark/Documents/GitHub/BilingualScriptureIOS/App Store/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A87BDFFB-543C-C44C-9AD7-FB4B70F630CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C33FAB-5F08-BC41-BA2C-170D6910B50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="500" windowWidth="28040" windowHeight="17440" xr2:uid="{7C034801-685D-B84A-97F6-445D3D70CDEE}"/>
+    <workbookView xWindow="-32620" yWindow="1380" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{7C034801-685D-B84A-97F6-445D3D70CDEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>eng</t>
   </si>
@@ -137,6 +138,77 @@
 	•	喜愛聆聽或需要語音支援的使用者
 	•	進行多語聖經研讀的人群
 立即下載，無論你身在何處，都能以心中熟悉的語言平靜地探索神的話語，享受清晰、舒適、溫柔的聖經體驗。</t>
+  </si>
+  <si>
+    <t>- Adopted to ios 26 language code (zh-HK to yue-HK)
+- Improved ios 26 animation performance
+- Cached scripture for better loading performance</t>
+  </si>
+  <si>
+    <t>聆听英文、中文等多种语言的圣经内容，配有清晰的语音朗读。操作简便，适合每日读经与灵性成长。</t>
+  </si>
+  <si>
+    <t>Chinese (Traditional)</t>
+  </si>
+  <si>
+    <t>Écoutez la Bible en anglais, chinois et plus, avec une voix claire. Facile à utiliser, parfait pour lire les Écritures et grandir spirituellement.</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>英語、中国語など多言語で聖書をクリアな音声で朗読。簡単に使えて、毎日の聖書朗読と霊的成長に最適です。</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>영어, 중국어 등 다양한 언어로 성경을 또렷한 음성으로 들을 수 있습니다. 사용이 간편하며, 매일의 성경 읽기와 영적 성장에 도움이 됩니다.</t>
+  </si>
+  <si>
+    <t>Escucha la Biblia en inglés, chino y más idiomas con narración clara. Fácil de usar y perfecto para la lectura diaria y el crecimiento espiritual.</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	Adaptation au code de langue iOS 26 (de zh-HK à yue-HK)
+	•	Amélioration des performances d’animation sous iOS 26
+	•	Mise en cache des écritures pour un chargement plus rapide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	iOS 26 の言語コードに対応（zh-HK から yue-HK へ）
+	•	iOS 26 のアニメーション性能を改善
+	•	聖句をキャッシュして読み込み速度を向上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	iOS 26 언어 코드 적용 (zh-HK → yue-HK)
+	•	iOS 26 애니메이션 성능 개선
+	•	경전을 캐싱하여 로딩 성능 향상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	Adaptado al código de idioma de iOS 26 (de zh-HK a yue-HK)
+	•	Mejora del rendimiento de animaciones en iOS 26
+	•	Escrituras en caché para un mejor rendimiento de carga</t>
+  </si>
+  <si>
+    <t>Chinese (Simplified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	采用 iOS 26 语言代码（从 zh-HK 改为 yue-HK）
+	•	改进 iOS 26 的动画性能
+	•	缓存经文以提升加载性能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	採用 iOS 26 語言代碼（由 zh-HK 改為 yue-HK）
+	•	改善 iOS 26 的動畫效能
+	•	緩存經文以提升載入效能</t>
   </si>
 </sst>
 </file>
@@ -184,11 +256,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,92 +584,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -616,6 +667,99 @@
       </c>
       <c r="C7" t="s">
         <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F204364A-76DC-894D-8806-39C338CDEC2A}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="111.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
